--- a/templates/record_result.xlsx
+++ b/templates/record_result.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/congdat/Developer/lab-admin-go/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8C3C0B4-5154-AA4C-98AE-285B21E24495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824F1623-CE92-0C4D-8D86-C092EFA8B97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="2300" windowWidth="27640" windowHeight="16940" xr2:uid="{8B3FE65E-164A-D14A-9CD4-4E8BC7E23AF0}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="27640" windowHeight="16940" xr2:uid="{8B3FE65E-164A-D14A-9CD4-4E8BC7E23AF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,18 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>PHÒNG XÉT NGHIỆM Y KHOA ANH QUÂN</t>
   </si>
   <si>
     <t>60 Đống Đa, Phường 2, TP. Cao Lãnh, Đồng Tháp</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Giới tính:</t>
   </si>
   <si>
     <t>Năm sinh:</t>
@@ -56,31 +50,30 @@
     <t>Họ tên:</t>
   </si>
   <si>
-    <t>Chuẩn đoán:</t>
-  </si>
-  <si>
     <t>Địa chỉ:</t>
-  </si>
-  <si>
-    <t>Ngày:</t>
-  </si>
-  <si>
-    <t>Số điện thoại:</t>
   </si>
   <si>
     <t>PHIẾU KẾT QUẢ XÉT NGHIÊM</t>
   </si>
   <si>
-    <t>Tên xét nghiệm</t>
+    <t>STT
+(No)</t>
   </si>
   <si>
-    <t>Kết quả</t>
+    <t>ĐVT
+(Unit)</t>
   </si>
   <si>
-    <t>ĐVT</t>
+    <t>KHOẢNG THAM CHIẾU
+(References)</t>
   </si>
   <si>
-    <t>KHOẢNG THAM CHIẾU</t>
+    <t>TÊN XÉT NGHIỆM
+(Test)</t>
+  </si>
+  <si>
+    <t>KẾT QUẢ
+(Result)</t>
   </si>
 </sst>
 </file>
@@ -96,35 +89,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow (Body)"/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="22"/>
       <color theme="1"/>
-      <name val="Aptos Narrow (Body)"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -162,33 +156,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -524,126 +542,1107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E100AF-50A7-C14A-943E-6B963B0CA7CB}">
-  <dimension ref="A1:E11"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5" customWidth="1"/>
-    <col min="2" max="2" width="43.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+    </row>
+    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="D9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" ht="22" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-    </row>
+    </row>
+    <row r="10" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="14"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="14"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="14"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+    </row>
+    <row r="13" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="14"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+    </row>
+    <row r="14" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="14"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+    </row>
+    <row r="15" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="14"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="14"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+    </row>
+    <row r="17" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="14"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="14"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+    </row>
+    <row r="19" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="14"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+    </row>
+    <row r="20" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="14"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+    </row>
+    <row r="21" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="14"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="14"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+    </row>
+    <row r="23" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="14"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="14"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+    </row>
+    <row r="25" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="14"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+    </row>
+    <row r="26" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="14"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+    </row>
+    <row r="27" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="14"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+    </row>
+    <row r="28" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="14"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+    </row>
+    <row r="29" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="14"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+    </row>
+    <row r="30" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="14"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+    </row>
+    <row r="31" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="14"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+    </row>
+    <row r="32" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="15"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+    </row>
+    <row r="33" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+    </row>
+    <row r="34" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="15"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+    </row>
+    <row r="35" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="15"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+    </row>
+    <row r="36" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="15"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+    </row>
+    <row r="37" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="15"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+    </row>
+    <row r="38" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="15"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+    </row>
+    <row r="39" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="15"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+    </row>
+    <row r="40" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="15"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+    </row>
+    <row r="41" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="15"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+    </row>
+    <row r="42" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="15"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+    </row>
+    <row r="43" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="15"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+    </row>
+    <row r="44" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="15"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+    </row>
+    <row r="45" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="15"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+    </row>
+    <row r="46" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="15"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+    </row>
+    <row r="47" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="15"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+    </row>
+    <row r="48" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="15"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+    </row>
+    <row r="49" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="15"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+    </row>
+    <row r="50" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="15"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+    </row>
+    <row r="51" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="15"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+    </row>
+    <row r="52" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="15"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+    </row>
+    <row r="53" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="15"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+    </row>
+    <row r="54" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="15"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+    </row>
+    <row r="55" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="15"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+    </row>
+    <row r="56" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="15"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+    </row>
+    <row r="57" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="15"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+    </row>
+    <row r="58" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="15"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
+    </row>
+    <row r="59" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="15"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+    </row>
+    <row r="60" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="15"/>
+      <c r="B60" s="16"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+    </row>
+    <row r="61" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="15"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+    </row>
+    <row r="62" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="15"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="15"/>
+    </row>
+    <row r="63" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="15"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="15"/>
+    </row>
+    <row r="64" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="15"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="15"/>
+    </row>
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="15"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
+    </row>
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="15"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+    </row>
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="15"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="15"/>
+    </row>
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="15"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="15"/>
+    </row>
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="15"/>
+      <c r="B69" s="16"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
+    </row>
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="15"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+    </row>
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="15"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+    </row>
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="15"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="15"/>
+    </row>
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="15"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="15"/>
+    </row>
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="15"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="15"/>
+    </row>
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="15"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
+    </row>
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="15"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="15"/>
+    </row>
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="15"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+    </row>
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="15"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+    </row>
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="15"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+    </row>
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="15"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+    </row>
+    <row r="81" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="15"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+    </row>
+    <row r="82" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="15"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="15"/>
+    </row>
+    <row r="83" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="15"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+    </row>
+    <row r="84" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="15"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="15"/>
+    </row>
+    <row r="85" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="15"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="15"/>
+      <c r="E85" s="15"/>
+    </row>
+    <row r="86" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="15"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="15"/>
+    </row>
+    <row r="87" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="15"/>
+      <c r="B87" s="16"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="15"/>
+    </row>
+    <row r="88" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="15"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="15"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="15"/>
+    </row>
+    <row r="89" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="15"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="15"/>
+    </row>
+    <row r="90" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="15"/>
+      <c r="B90" s="16"/>
+    </row>
+    <row r="91" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="15"/>
+      <c r="B91" s="16"/>
+    </row>
+    <row r="92" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="15"/>
+      <c r="B92" s="16"/>
+    </row>
+    <row r="93" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="15"/>
+      <c r="B93" s="16"/>
+    </row>
+    <row r="94" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="15"/>
+      <c r="B94" s="16"/>
+    </row>
+    <row r="95" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="15"/>
+      <c r="B95" s="16"/>
+    </row>
+    <row r="96" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="15"/>
+      <c r="B96" s="16"/>
+    </row>
+    <row r="97" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="15"/>
+      <c r="B97" s="16"/>
+    </row>
+    <row r="98" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="15"/>
+      <c r="B98" s="16"/>
+    </row>
+    <row r="99" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="15"/>
+      <c r="B99" s="16"/>
+    </row>
+    <row r="100" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="15"/>
+      <c r="B100" s="16"/>
+    </row>
+    <row r="101" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="15"/>
+      <c r="B101" s="16"/>
+    </row>
+    <row r="102" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="15"/>
+      <c r="B102" s="16"/>
+    </row>
+    <row r="103" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="15"/>
+      <c r="B103" s="16"/>
+    </row>
+    <row r="104" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="15"/>
+      <c r="B104" s="16"/>
+    </row>
+    <row r="105" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="15"/>
+      <c r="B105" s="16"/>
+    </row>
+    <row r="106" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="15"/>
+      <c r="B106" s="16"/>
+    </row>
+    <row r="107" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="15"/>
+      <c r="B107" s="16"/>
+    </row>
+    <row r="108" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="15"/>
+      <c r="B108" s="16"/>
+    </row>
+    <row r="109" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="15"/>
+      <c r="B109" s="16"/>
+    </row>
+    <row r="110" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="15"/>
+      <c r="B110" s="16"/>
+    </row>
+    <row r="111" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="15"/>
+      <c r="B111" s="16"/>
+    </row>
+    <row r="112" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="15"/>
+      <c r="B112" s="16"/>
+    </row>
+    <row r="113" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="15"/>
+      <c r="B113" s="16"/>
+    </row>
+    <row r="114" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="15"/>
+      <c r="B114" s="16"/>
+    </row>
+    <row r="115" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="15"/>
+      <c r="B115" s="16"/>
+    </row>
+    <row r="116" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="15"/>
+      <c r="B116" s="16"/>
+    </row>
+    <row r="117" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="15"/>
+      <c r="B117" s="16"/>
+    </row>
+    <row r="118" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="15"/>
+      <c r="B118" s="16"/>
+    </row>
+    <row r="119" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="15"/>
+      <c r="B119" s="16"/>
+    </row>
+    <row r="120" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="15"/>
+      <c r="B120" s="16"/>
+    </row>
+    <row r="121" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="15"/>
+      <c r="B121" s="16"/>
+    </row>
+    <row r="122" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="15"/>
+      <c r="B122" s="16"/>
+    </row>
+    <row r="123" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="15"/>
+      <c r="B123" s="16"/>
+    </row>
+    <row r="124" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="15"/>
+      <c r="B124" s="16"/>
+    </row>
+    <row r="125" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="15"/>
+      <c r="B125" s="16"/>
+    </row>
+    <row r="126" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="15"/>
+      <c r="B126" s="16"/>
+    </row>
+    <row r="127" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="15"/>
+      <c r="B127" s="16"/>
+    </row>
+    <row r="128" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="15"/>
+      <c r="B128" s="16"/>
+    </row>
+    <row r="129" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="15"/>
+      <c r="B129" s="16"/>
+    </row>
+    <row r="130" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="15"/>
+      <c r="B130" s="16"/>
+    </row>
+    <row r="131" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="15"/>
+      <c r="B131" s="16"/>
+    </row>
+    <row r="132" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="15"/>
+      <c r="B132" s="16"/>
+    </row>
+    <row r="133" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="15"/>
+      <c r="B133" s="16"/>
+    </row>
+    <row r="134" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="15"/>
+      <c r="B134" s="16"/>
+    </row>
+    <row r="135" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="15"/>
+      <c r="B135" s="16"/>
+    </row>
+    <row r="136" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="15"/>
+      <c r="B136" s="16"/>
+    </row>
+    <row r="137" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="15"/>
+      <c r="B137" s="16"/>
+    </row>
+    <row r="138" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="15"/>
+      <c r="B138" s="16"/>
+    </row>
+    <row r="139" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="15"/>
+      <c r="B139" s="16"/>
+    </row>
+    <row r="140" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="15"/>
+      <c r="B140" s="16"/>
+    </row>
+    <row r="141" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="15"/>
+      <c r="B141" s="16"/>
+    </row>
+    <row r="142" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="15"/>
+      <c r="B142" s="16"/>
+    </row>
+    <row r="143" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="15"/>
+      <c r="B143" s="16"/>
+    </row>
+    <row r="144" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="15"/>
+      <c r="B144" s="16"/>
+    </row>
+    <row r="145" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="15"/>
+      <c r="B145" s="16"/>
+    </row>
+    <row r="146" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="15"/>
+      <c r="B146" s="16"/>
+    </row>
+    <row r="147" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="15"/>
+      <c r="B147" s="16"/>
+    </row>
+    <row r="148" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="15"/>
+      <c r="B148" s="16"/>
+    </row>
+    <row r="149" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="15"/>
+      <c r="B149" s="16"/>
+    </row>
+    <row r="150" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="15"/>
+      <c r="B150" s="16"/>
+    </row>
+    <row r="151" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="15"/>
+      <c r="B151" s="16"/>
+    </row>
+    <row r="152" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="15"/>
+      <c r="B152" s="16"/>
+    </row>
+    <row r="153" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="15"/>
+      <c r="B153" s="16"/>
+    </row>
+    <row r="154" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="15"/>
+      <c r="B154" s="16"/>
+    </row>
+    <row r="155" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="15"/>
+      <c r="B155" s="16"/>
+    </row>
+    <row r="156" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="15"/>
+      <c r="B156" s="16"/>
+    </row>
+    <row r="157" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="15"/>
+      <c r="B157" s="16"/>
+    </row>
+    <row r="158" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="15"/>
+      <c r="B158" s="16"/>
+    </row>
+    <row r="159" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="15"/>
+      <c r="B159" s="16"/>
+    </row>
+    <row r="160" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="15"/>
+      <c r="B160" s="16"/>
+    </row>
+    <row r="161" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="15"/>
+      <c r="B161" s="16"/>
+    </row>
+    <row r="162" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="15"/>
+      <c r="B162" s="16"/>
+    </row>
+    <row r="163" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="15"/>
+      <c r="B163" s="16"/>
+    </row>
+    <row r="164" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="15"/>
+      <c r="B164" s="16"/>
+    </row>
+    <row r="165" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="15"/>
+      <c r="B165" s="16"/>
+    </row>
+    <row r="166" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="15"/>
+      <c r="B166" s="16"/>
+    </row>
+    <row r="167" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="15"/>
+      <c r="B167" s="16"/>
+    </row>
+    <row r="168" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="15"/>
+      <c r="B168" s="16"/>
+    </row>
+    <row r="169" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="15"/>
+      <c r="B169" s="16"/>
+    </row>
+    <row r="170" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="15"/>
+      <c r="B170" s="16"/>
+    </row>
+    <row r="171" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="15"/>
+      <c r="B171" s="16"/>
+    </row>
+    <row r="172" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="15"/>
+      <c r="B172" s="16"/>
+    </row>
+    <row r="173" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="15"/>
+      <c r="B173" s="16"/>
+    </row>
+    <row r="174" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="15"/>
+      <c r="B174" s="16"/>
+    </row>
+    <row r="175" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="15"/>
+      <c r="B175" s="16"/>
+    </row>
+    <row r="176" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="15"/>
+      <c r="B176" s="16"/>
+    </row>
+    <row r="177" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="15"/>
+      <c r="B177" s="16"/>
+    </row>
+    <row r="178" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="15"/>
+      <c r="B178" s="16"/>
+    </row>
+    <row r="179" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="15"/>
+      <c r="B179" s="16"/>
+    </row>
+    <row r="180" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="15"/>
+      <c r="B180" s="16"/>
+    </row>
+    <row r="181" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="15"/>
+      <c r="B181" s="16"/>
+    </row>
+    <row r="182" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="15"/>
+      <c r="B182" s="16"/>
+    </row>
+    <row r="183" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="15"/>
+      <c r="B183" s="16"/>
+    </row>
+    <row r="184" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="15"/>
+      <c r="B184" s="16"/>
+    </row>
+    <row r="185" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="15"/>
+      <c r="B185" s="16"/>
+    </row>
+    <row r="186" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="15"/>
+      <c r="B186" s="16"/>
+    </row>
+    <row r="187" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="15"/>
+      <c r="B187" s="16"/>
+    </row>
+    <row r="188" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="15"/>
+      <c r="B188" s="16"/>
+    </row>
+    <row r="189" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="15"/>
+      <c r="B189" s="16"/>
+    </row>
+    <row r="190" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="15"/>
+      <c r="B190" s="16"/>
+    </row>
+    <row r="191" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="15"/>
+      <c r="B191" s="16"/>
+    </row>
+    <row r="192" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="15"/>
+      <c r="B192" s="16"/>
+    </row>
+    <row r="193" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="15"/>
+      <c r="B193" s="16"/>
+    </row>
+    <row r="194" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="15"/>
+    </row>
+    <row r="195" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="15"/>
+    </row>
+    <row r="196" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="15"/>
+    </row>
+    <row r="197" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="15"/>
+    </row>
+    <row r="198" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B8:E8"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="79" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>